--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,160 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Check Caption on Amazon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Create Bundle Link</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Work with Aman on Klaviyo Integration</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Review Mailer Creation Document</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>To ensure the mailer creation is done correctly and on time.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -499,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -557,6 +711,159 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Check Caption on Amazon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Create Bundle Link</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Work with Aman on Klaviyo Integration</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Review Mailer Creation Document</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>To ensure the mailer creation is done correctly and on time.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Today</t>
         </is>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -427,18 +427,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,30 +460,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Why We're Doing This</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Growth Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SPOC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Go Live</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -506,20 +512,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Accurate product information is crucial for customer satisfaction and trust.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -543,20 +554,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -580,20 +596,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Chat | with Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Anchit Tandon</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -617,25 +638,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Chat | with Anchit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>To ensure the mailer creation is done correctly and on time.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Anchit</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
@@ -659,25 +685,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>As per calendar sheet</t>
         </is>
@@ -701,20 +732,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -738,20 +774,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -775,20 +816,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -812,25 +858,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Before Mother's Day</t>
         </is>
@@ -854,25 +905,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>To grab customers' attention and increase email open rates.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Before sending Mother's Day emails</t>
         </is>
@@ -896,25 +952,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Increase sales and revenue by promoting a high-demand product.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Go Live</t>
         </is>
@@ -938,20 +999,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>To understand the current email marketing strategy and identify areas for improvement.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -975,20 +1041,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>To ensure a smooth customer experience and minimize cancellations.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1012,20 +1083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>To document the current state of email marketing campaigns.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1049,20 +1125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Chat | with Anchit</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Anchit</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1086,20 +1167,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>To maintain a record of current email flows and data for future reference and improvement.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1123,20 +1209,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1160,20 +1251,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>To increase average order value and encourage users to explore more products.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1197,20 +1293,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>To increase sales and improve customer satisfaction.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1234,20 +1335,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>To improve customer satisfaction and reduce support queries.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1271,20 +1377,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Chat | with Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>To get a clear understanding of the agency's services and fees.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Anchit Tandon</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1308,20 +1419,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>To ensure seamless collaboration and minimize potential issues.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1345,20 +1461,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>To ensure transparency and clarity in the agency's fees.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1382,20 +1503,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>To ensure the content is ready for use in the production environment.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1419,25 +1545,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>2 hours</t>
         </is>
@@ -1461,20 +1592,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1498,20 +1634,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1535,25 +1676,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>To improve conversion rates on the UK website.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1577,25 +1723,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>To improve the user experience for Canadian customers.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1619,25 +1770,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Chat | with Arihant</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>To improve customer engagement and retention.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Arihant</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1661,30 +1817,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Anchit needs this data for analysis and decision-making.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>As soon as possible</t>
         </is>
@@ -1708,25 +1869,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1750,25 +1916,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Chat | with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>users/101892413922856052375</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1792,25 +1963,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1834,30 +2010,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Meeting | speaker Anchit</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>App creation is a priority to move forward with new features and revenue growth.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Anshith</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>by the weekend</t>
         </is>
@@ -1881,25 +2062,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1923,25 +2109,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Address the user's concern to provide a good customer experience.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1965,25 +2156,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>Chat | with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Anchit needs this checked to move forward.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>users/112363631041538884730</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2007,30 +2203,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Meet the user's request to send the file today.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
@@ -2054,30 +2255,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>The recipient is waiting for the item to be shared.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>by night</t>
         </is>
@@ -2101,25 +2307,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Chat | with Subham</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>This will help Subham understand the process and requirements for opening a salary account.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Subham</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2143,30 +2354,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Need to discuss something with Aman.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>As soon as possible</t>
         </is>
@@ -2190,25 +2406,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Chat | with Subham</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Anchit needs to stay informed about the topic.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Subham</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2232,25 +2453,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Chat | with Shehzad</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Installing Claude requires the admin account password to proceed.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Shahzad</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2274,31 +2500,76 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Chat | with Shehzad</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Anchit needs access to the vtadmin password for work.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Shehzad</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Develop an automated project to track and check various aspects of the business.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>To improve efficiency and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2311,18 +2582,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2343,30 +2615,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Why We're Doing This</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Growth Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SPOC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Go Live</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -2390,20 +2667,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Accurate product information is crucial for customer satisfaction and trust.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2427,20 +2709,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2464,20 +2751,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Chat | with Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Anchit Tandon</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2501,25 +2793,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Chat | with Anchit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>To ensure the mailer creation is done correctly and on time.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Anchit</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
@@ -2543,25 +2840,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>As per calendar sheet</t>
         </is>
@@ -2585,20 +2887,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2622,20 +2929,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2659,20 +2971,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2696,25 +3013,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Before Mother's Day</t>
         </is>
@@ -2738,25 +3060,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>To grab customers' attention and increase email open rates.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Before sending Mother's Day emails</t>
         </is>
@@ -2780,25 +3107,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Increase sales and revenue by promoting a high-demand product.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Go Live</t>
         </is>
@@ -2822,20 +3154,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>To understand the current email marketing strategy and identify areas for improvement.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2859,20 +3196,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>To ensure a smooth customer experience and minimize cancellations.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2896,20 +3238,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>To document the current state of email marketing campaigns.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2933,20 +3280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Chat | with Anchit</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Anchit</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2970,20 +3322,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>To maintain a record of current email flows and data for future reference and improvement.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3007,20 +3364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3044,20 +3406,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>To increase average order value and encourage users to explore more products.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3081,20 +3448,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>To increase sales and improve customer satisfaction.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3118,20 +3490,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Chat | with users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>To improve customer satisfaction and reduce support queries.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>users/110152155675645013355</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3155,20 +3532,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Chat | with Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>To get a clear understanding of the agency's services and fees.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Anchit Tandon</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3192,20 +3574,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>To ensure seamless collaboration and minimize potential issues.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3229,20 +3616,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>To ensure transparency and clarity in the agency's fees.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3266,20 +3658,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>To ensure the content is ready for use in the production environment.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3303,25 +3700,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>2 hours</t>
         </is>
@@ -3345,20 +3747,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3382,20 +3789,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3419,25 +3831,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>To improve conversion rates on the UK website.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3461,25 +3878,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Chat | with Manisha</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>To improve the user experience for Canadian customers.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Manisha</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3503,25 +3925,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Chat | with Arihant</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>To improve customer engagement and retention.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Arihant</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3545,30 +3972,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Anchit needs this data for analysis and decision-making.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>As soon as possible</t>
         </is>
@@ -3592,25 +4024,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3634,25 +4071,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Chat | with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>users/101892413922856052375</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3676,25 +4118,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3718,30 +4165,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Meeting | speaker Anchit</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>App creation is a priority to move forward with new features and revenue growth.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Anshith</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>by the weekend</t>
         </is>
@@ -3765,25 +4217,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3807,25 +4264,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Address the user's concern to provide a good customer experience.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3849,25 +4311,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>Chat | with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Anchit needs this checked to move forward.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>users/112363631041538884730</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3891,30 +4358,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Meet the user's request to send the file today.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
@@ -3938,30 +4410,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>Chat | with Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>The recipient is waiting for the item to be shared.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Anchit (Self)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>by night</t>
         </is>
@@ -3985,25 +4462,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Chat | with Subham</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>This will help Subham understand the process and requirements for opening a salary account.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Subham</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4027,30 +4509,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Chat | with Aman</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Need to discuss something with Aman.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>As soon as possible</t>
         </is>
@@ -4074,25 +4561,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Chat | with Subham</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Anchit needs to stay informed about the topic.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Subham</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4116,25 +4608,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Chat | with Shehzad</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Installing Claude requires the admin account password to proceed.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Team &amp; Process</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Shahzad</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4158,25 +4655,114 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Chat | with Shehzad</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Chat | DM</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Anchit needs access to the vtadmin password for work.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Shehzad</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Develop an automated project to track and check various aspects of the business.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>To improve efficiency and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Develop an automated project to track and check various aspects of the business.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>To improve efficiency and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4193,18 +4779,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4225,30 +4812,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Why We're Doing This</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Growth Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SPOC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Go Live</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -745,11 +745,6 @@
           <t>Brand &amp; Content</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -792,11 +787,6 @@
           <t>Brand &amp; Content</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -985,11 +975,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1032,11 +1017,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1079,11 +1059,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1589,11 +1564,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1636,11 +1606,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1965,11 +1930,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>High</t>
@@ -2012,11 +1972,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2059,11 +2014,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2388,11 +2338,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>High</t>
@@ -2435,11 +2380,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>High</t>
@@ -2482,11 +2422,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>High</t>
@@ -2529,11 +2464,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>High</t>
@@ -2764,11 +2694,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3004,11 +2929,6 @@
           <t>Retention</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3051,11 +2971,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Low</t>
@@ -3192,11 +3107,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3521,11 +3431,6 @@
           <t>Retention</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3582,12 +3487,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Review and Optimize Email Sends</t>
+          <t>Update Product Listings and Availability</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Review the email sends schedule and optimize for better engagement and conversion rates, ensuring no one gets spammed.</t>
+          <t>Update the product listings and availability on the website and Amazon to ensure that customers can easily find and purchase the products mentioned in the email campaign.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3602,39 +3507,39 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.489186+00:00</t>
+          <t>2026-05-08T22:29:09.511333+00:00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>To maximize the impact of the email sprint and achieve the desired revenue goals.</t>
+          <t>To ensure a seamless customer experience and maximize sales opportunities.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monitor and Analyze Email Performance</t>
+          <t>Design the email campaign</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Monitor the email performance and analyze the results to identify areas of improvement and optimize future email campaigns.</t>
+          <t>Create a premium email campaign for VAHDAM India targeting UK customers to drive replenishment and AOV lift by promoting 2-pack bundles.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3649,17 +3554,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.500539+00:00</t>
+          <t>2026-05-08T22:29:41.875777+00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>To understand the effectiveness of the email sprint and make data-driven decisions for future campaigns.</t>
+          <t>Increase customer convenience and drive sales by promoting 2-pack bundles.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3669,19 +3574,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Update Product Listings and Availability</t>
+          <t>Finalize product selection</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Update the product listings and availability on the website and Amazon to ensure that customers can easily find and purchase the products mentioned in the email campaign.</t>
+          <t>Select the two products to feature in the email campaign (Turmeric Ashwagandha 100 Tea Bags and Turmeric Ginger 100 Tea Bags).</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3696,17 +3601,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.511333+00:00</t>
+          <t>2026-05-08T22:29:41.881891+00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>To ensure a seamless customer experience and maximize sales opportunities.</t>
+          <t>Ensure the products are relevant and appealing to the target audience.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3716,19 +3621,19 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Design the email campaign</t>
+          <t>Create a compelling subject line</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Create a premium email campaign for VAHDAM India targeting UK customers to drive replenishment and AOV lift by promoting 2-pack bundles.</t>
+          <t>Craft a subject line that effectively communicates the value proposition of the 2-pack bundle.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3743,12 +3648,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.875777+00:00</t>
+          <t>2026-05-08T22:29:41.886538+00:00</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Increase customer convenience and drive sales by promoting 2-pack bundles.</t>
+          <t>Increase email open rates and drive engagement.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3758,7 +3663,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Arihant</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3770,12 +3675,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Finalize product selection</t>
+          <t>Create premium DTC email for VAHDAM India (UK market)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Select the two products to feature in the email campaign (Turmeric Ashwagandha 100 Tea Bags and Turmeric Ginger 100 Tea Bags).</t>
+          <t>Design and send a targeted email campaign to active buyers in the UK market, promoting the new iced tea range and highlighting its exclusivity on the VAHDAM website.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3790,39 +3695,44 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.881891+00:00</t>
+          <t>2026-05-08T22:30:00.635644+00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ensure the products are relevant and appealing to the target audience.</t>
+          <t>Drive incremental seasonal purchases from active buyers in the UK market by introducing the new iced tea range and creating a sense of exclusivity.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Create a compelling subject line</t>
+          <t>Check Caption on Amazon</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Craft a subject line that effectively communicates the value proposition of the 2-pack bundle.</t>
+          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3837,22 +3747,22 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.886538+00:00</t>
+          <t>2026-05-08T22:30:53.742095+00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Increase email open rates and drive engagement.</t>
+          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Arihant</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3864,12 +3774,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Create premium DTC email for VAHDAM India (UK market)</t>
+          <t>Create Bundle Link</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Design and send a targeted email campaign to active buyers in the UK market, promoting the new iced tea range and highlighting its exclusivity on the VAHDAM website.</t>
+          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3884,44 +3794,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-08T22:30:00.635644+00:00</t>
+          <t>2026-05-08T22:31:06.340431+00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Drive incremental seasonal purchases from active buyers in the UK market by introducing the new iced tea range and creating a sense of exclusivity.</t>
+          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Check Caption on Amazon</t>
+          <t>Work with Aman on Klaviyo Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
+          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3936,39 +3841,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-08T22:30:53.742095+00:00</t>
+          <t>2026-05-08T22:31:29.184257+00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
+          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit Tandon</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Create Bundle Link</t>
+          <t>Review Mailer Creation Document</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
+          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3983,12 +3888,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-08T22:31:06.340431+00:00</t>
+          <t>2026-05-08T22:32:31.890128+00:00</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
+          <t>To ensure the mailer creation is done correctly and on time.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3998,24 +3903,29 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Work with Aman on Klaviyo Integration</t>
+          <t>Send 1st mailer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
+          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4030,12 +3940,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08T22:31:29.184257+00:00</t>
+          <t>2026-05-08T22:33:33.782561+00:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
+          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4045,24 +3955,29 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>As per calendar sheet</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Review Mailer Creation Document</t>
+          <t>Fix Product Page Alignment</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
+          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4077,44 +3992,39 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-08T22:32:31.890128+00:00</t>
+          <t>2026-05-08T22:34:13.184575+00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>To ensure the mailer creation is done correctly and on time.</t>
+          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Send 1st mailer</t>
+          <t>Correct Grammar in Product Selection</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
+          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4129,17 +4039,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-08T22:33:33.782561+00:00</t>
+          <t>2026-05-08T22:34:13.194823+00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
+          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4149,24 +4059,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>As per calendar sheet</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Fix Product Page Alignment</t>
+          <t>Fix Broken CTAs</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
+          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4181,12 +4086,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.184575+00:00</t>
+          <t>2026-05-08T22:34:13.207312+00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
+          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4208,12 +4113,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Correct Grammar in Product Selection</t>
+          <t>Finalize Mother's Day Gift Ideas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
+          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4228,17 +4133,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.194823+00:00</t>
+          <t>2026-05-08T22:34:24.039065+00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
+          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4249,18 +4154,23 @@
       <c r="K79" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Before Mother's Day</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fix Broken CTAs</t>
+          <t>Create Email Subject Lines</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
+          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4275,39 +4185,44 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.207312+00:00</t>
+          <t>2026-05-08T22:34:24.049162+00:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
+          <t>To grab customers' attention and increase email open rates.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Before sending Mother's Day emails</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Finalize Mother's Day Gift Ideas</t>
+          <t>Finalize Email Campaign for First Flush Tea</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
+          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4322,17 +4237,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:24.039065+00:00</t>
+          <t>2026-05-08T22:34:52.148970+00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
+          <t>Increase sales and revenue by promoting a high-demand product.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4347,19 +4262,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Before Mother's Day</t>
+          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Create Email Subject Lines</t>
+          <t>Review UK Consumer Emails</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
+          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4374,44 +4289,39 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:24.049162+00:00</t>
+          <t>2026-05-08T22:35:34.120456+00:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>To grab customers' attention and increase email open rates.</t>
+          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Before sending Mother's Day emails</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Finalize Email Campaign for First Flush Tea</t>
+          <t>Review Cancellation Flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
+          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4426,17 +4336,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:52.148970+00:00</t>
+          <t>2026-05-08T22:35:34.131514+00:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Increase sales and revenue by promoting a high-demand product.</t>
+          <t>To ensure a smooth customer experience and minimize cancellations.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4446,24 +4356,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Go Live</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Review UK Consumer Emails</t>
+          <t>Take Screenshots of Campaigns</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
+          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4478,12 +4383,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.120456+00:00</t>
+          <t>2026-05-08T22:35:34.139460+00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
+          <t>To document the current state of email marketing campaigns.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4505,12 +4410,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Review Cancellation Flow</t>
+          <t>Verify Hibiscus Rose Discount Consistency</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
+          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4525,39 +4430,39 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.131514+00:00</t>
+          <t>2026-05-08T22:35:46.978363+00:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>To ensure a smooth customer experience and minimize cancellations.</t>
+          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Take Screenshots of Campaigns</t>
+          <t>Retain Email Flow Documentation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
+          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4572,12 +4477,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.139460+00:00</t>
+          <t>2026-05-08T22:35:56.509833+00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>To document the current state of email marketing campaigns.</t>
+          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4587,7 +4492,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4599,12 +4504,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Verify Hibiscus Rose Discount Consistency</t>
+          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
+          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4619,39 +4524,34 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:46.978363+00:00</t>
+          <t>2026-05-08T22:36:05.582729+00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
+          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Anchit</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Retain Email Flow Documentation</t>
+          <t>Implement nudges on Vahdam India's PDP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
+          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4666,22 +4566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:56.509833+00:00</t>
+          <t>2026-05-08T22:36:05.597638+00:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
+          <t>To increase average order value and encourage users to explore more products.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Retention</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Manisha</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4693,12 +4588,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
+          <t>Develop a recommendation engine for Vahdam India's website</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
+          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4713,22 +4608,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.582729+00:00</t>
+          <t>2026-05-08T22:36:05.606317+00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
+          <t>To increase sales and improve customer satisfaction.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4740,12 +4630,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Implement nudges on Vahdam India's PDP</t>
+          <t>Analyze customer support queries to identify areas for improvement</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
+          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4760,22 +4650,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.597638+00:00</t>
+          <t>2026-05-08T22:36:05.612573+00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>To increase average order value and encourage users to explore more products.</t>
+          <t>To improve customer satisfaction and reduce support queries.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>AOV</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4787,12 +4672,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Develop a recommendation engine for Vahdam India's website</t>
+          <t>Request for Quote (RFQ)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
+          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4807,22 +4692,22 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.606317+00:00</t>
+          <t>2026-05-08T22:36:56.953122+00:00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>To increase sales and improve customer satisfaction.</t>
+          <t>To get a clear understanding of the agency's services and fees.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>users/110152155675645013355</t>
+          <t>Anchit Tandon</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4834,12 +4719,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Analyze customer support queries to identify areas for improvement</t>
+          <t>Discuss View-Only Access with Agency</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
+          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4854,22 +4739,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.612573+00:00</t>
+          <t>2026-05-08T22:36:56.961722+00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>To improve customer satisfaction and reduce support queries.</t>
+          <t>To ensure seamless collaboration and minimize potential issues.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>users/110152155675645013355</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4881,12 +4766,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Request for Quote (RFQ)</t>
+          <t>Prepare Quotation Slab</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
+          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4901,12 +4786,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.953122+00:00</t>
+          <t>2026-05-08T22:36:56.967275+00:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>To get a clear understanding of the agency's services and fees.</t>
+          <t>To ensure transparency and clarity in the agency's fees.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4916,7 +4801,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4928,12 +4813,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Discuss View-Only Access with Agency</t>
+          <t>Create Production-Ready HTML</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
+          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4948,17 +4833,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.961722+00:00</t>
+          <t>2026-05-08T22:39:50.956188+00:00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>To ensure seamless collaboration and minimize potential issues.</t>
+          <t>To ensure the content is ready for use in the production environment.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4975,12 +4860,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Prepare Quotation Slab</t>
+          <t>Set 2-hour timer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
+          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4995,17 +4880,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.967275+00:00</t>
+          <t>2026-05-08T22:40:15.847487+00:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>To ensure transparency and clarity in the agency's fees.</t>
+          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5016,18 +4901,23 @@
       <c r="K95" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2 hours</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Create Production-Ready HTML</t>
+          <t>Host Images on Shopify</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
+          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5042,17 +4932,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-08T22:39:50.956188+00:00</t>
+          <t>2026-05-08T22:40:35.933949+00:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>To ensure the content is ready for use in the production environment.</t>
+          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5062,19 +4952,19 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Set 2-hour timer</t>
+          <t>Host HTMLs on Shopify</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
+          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5089,17 +4979,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-08T22:40:15.847487+00:00</t>
+          <t>2026-05-08T22:41:13.063844+00:00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
+          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5110,23 +5000,18 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>2 hours</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Host Images on Shopify</t>
+          <t>Review UK Landing Pages</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
+          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5136,22 +5021,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Chat | Google Chat</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-08T22:40:35.933949+00:00</t>
+          <t>2026-05-08T22:43:53.526856+00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
+          <t>To improve conversion rates on the UK website.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5161,19 +5046,19 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Host HTMLs on Shopify</t>
+          <t>Update Canada-Specific Content</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
+          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5183,27 +5068,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Chat | Google Chat</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-08T22:41:13.063844+00:00</t>
+          <t>2026-05-08T22:43:53.558663+00:00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
+          <t>To improve the user experience for Canadian customers.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5215,12 +5100,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Review UK Landing Pages</t>
+          <t>Review Nutrition Support Pages</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
+          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5235,39 +5120,39 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.526856+00:00</t>
+          <t>2026-05-08T22:43:53.570620+00:00</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>To improve conversion rates on the UK website.</t>
+          <t>To improve customer engagement and retention.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Arihant</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Update Canada-Specific Content</t>
+          <t>Provide UK Data in Specified Format</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
+          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5282,39 +5167,44 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.558663+00:00</t>
+          <t>2026-05-08T22:44:12.623888+00:00</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>To improve the user experience for Canadian customers.</t>
+          <t>Anchit needs this data for analysis and decision-making.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Review Nutrition Support Pages</t>
+          <t>Prepare Price Parity Sheet</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
+          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5324,44 +5214,49 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.570620+00:00</t>
+          <t>2026-05-08T22:45:13.665247+00:00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>To improve customer engagement and retention.</t>
+          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Arihant</t>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>101892413922856</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Provide UK Data in Specified Format</t>
+          <t>Update on Gorilla sheet</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
+          <t>Get an update on the current status of the Gorilla sheet.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5371,49 +5266,44 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-08T22:44:12.623888+00:00</t>
+          <t>2026-05-08T22:45:22.145961+00:00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Anchit needs this data for analysis and decision-making.</t>
+          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Aman</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>101892413922856</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>As soon as possible</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prepare Price Parity Sheet</t>
+          <t>Research Amazon Pricing</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
+          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5428,12 +5318,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:13.665247+00:00</t>
+          <t>2026-05-08T22:45:39.720118+00:00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
+          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5453,19 +5343,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Update on Gorilla sheet</t>
+          <t>Complete App Creation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Get an update on the current status of the Gorilla sheet.</t>
+          <t>Anchit needs to finish creating his app by the weekend.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5475,49 +5365,49 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Chat | DM with users/101892413922856052375</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:22.145961+00:00</t>
+          <t>2026-05-08T22:45:50.944684+00:00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
+          <t>App creation is a priority to move forward with new features and revenue growth.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>users/101892413922856052375</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>101892413922856</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>by the weekend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Research Amazon Pricing</t>
+          <t>Review Email List and Body</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
+          <t>Review the email list and body sent by the user and take necessary actions.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5527,22 +5417,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chat | DM with users/101892413922856052375</t>
+          <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:39.720118+00:00</t>
+          <t>2026-05-08T22:46:55.532712+00:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
+          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5552,7 +5442,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>101892413922856</t>
+          <t>112363631041538</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5564,12 +5454,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Complete App Creation</t>
+          <t>Follow up on user query</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Anchit needs to finish creating his app by the weekend.</t>
+          <t>Respond to the user's query in the DM.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5579,49 +5469,49 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
+          <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:50.944684+00:00</t>
+          <t>2026-05-08T22:47:18.396185+00:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>App creation is a priority to move forward with new features and revenue growth.</t>
+          <t>Address the user's concern to provide a good customer experience.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>112363631041538</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>by the weekend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Review Email List and Body</t>
+          <t>Check Something</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Review the email list and body sent by the user and take necessary actions.</t>
+          <t>The recipient needs to check something as requested by Anchit.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5636,22 +5526,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-08T22:46:55.532712+00:00</t>
+          <t>2026-05-08T22:47:30.899202+00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
+          <t>Anchit needs this checked to move forward.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Anchit (Self)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5668,12 +5553,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Follow up on user query</t>
+          <t>Send requested file</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Respond to the user's query in the DM.</t>
+          <t>Send the requested file to the user today.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5688,17 +5573,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:18.396185+00:00</t>
+          <t>2026-05-08T22:47:40.411387+00:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Address the user's concern to provide a good customer experience.</t>
+          <t>Meet the user's request to send the file today.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5714,18 +5599,23 @@
       <c r="K109" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Check Something</t>
+          <t>Share the item by night</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The recipient needs to check something as requested by Anchit.</t>
+          <t>Share the item with the recipient by the end of the day.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5740,12 +5630,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:30.899202+00:00</t>
+          <t>2026-05-08T22:48:07.925411+00:00</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anchit needs this checked to move forward.</t>
+          <t>The recipient is waiting for the item to be shared.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5755,7 +5645,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>users/112363631041538884730</t>
+          <t>Anchit (Self)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5766,18 +5656,23 @@
       <c r="K110" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>by night</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Send requested file</t>
+          <t>Follow up on salary account opening</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Send the requested file to the user today.</t>
+          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5787,17 +5682,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Chat | DM with users/112363631041538884730</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:40.411387+00:00</t>
+          <t>2026-05-08T22:48:35.348293+00:00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Meet the user's request to send the file today.</t>
+          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5807,34 +5702,24 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>112363631041538</t>
+          <t>Subham</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Today</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Share the item by night</t>
+          <t>Schedule Meeting</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Share the item with the recipient by the end of the day.</t>
+          <t>Schedule a meeting with Aman to discuss the same topic.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5844,32 +5729,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Chat | DM with users/112363631041538884730</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:07.925411+00:00</t>
+          <t>2026-05-08T22:48:42.866232+00:00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>The recipient is waiting for the item to be shared.</t>
+          <t>Need to discuss something with Aman.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>112363631041538</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5879,19 +5759,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>by night</t>
+          <t>As soon as possible</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Follow up on salary account opening</t>
+          <t>Update on Current Status</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
+          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5906,12 +5786,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:35.348293+00:00</t>
+          <t>2026-05-08T22:48:47.346443+00:00</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
+          <t>Anchit needs to stay informed about the topic.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5926,19 +5806,19 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Schedule Meeting</t>
+          <t>Provide VTAdmin account password</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Schedule a meeting with Aman to discuss the same topic.</t>
+          <t>Share the admin account password (VTAdmin) with Shehzad to help with installing Claude.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5953,12 +5833,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:42.866232+00:00</t>
+          <t>2026-05-08T22:48:54.415129+00:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Need to discuss something with Aman.</t>
+          <t>Installing Claude requires the admin account password to proceed.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5968,29 +5848,24 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Shehzad</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>As soon as possible</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Update on Current Status</t>
+          <t>Provide vtadmin password</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
+          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6005,22 +5880,22 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:47.346443+00:00</t>
+          <t>2026-05-08T22:49:45.147752+00:00</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anchit needs to stay informed about the topic.</t>
+          <t>Anchit needs access to the vtadmin password for work.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Subham</t>
+          <t>Shehzad</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6032,12 +5907,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Provide VTAdmin account password</t>
+          <t>Create Automated Tracker Project</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Share the admin account password (VTAdmin) with Shehzad to help with installing Claude.</t>
+          <t>Develop an automated project to track and check various aspects of the business.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6047,44 +5922,39 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:54.415129+00:00</t>
+          <t>2026-05-09T00:11:20.261831+00:00</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Installing Claude requires the admin account password to proceed.</t>
+          <t>To improve efficiency and reduce manual errors.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Shehzad</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Provide vtadmin password</t>
+          <t>Follow up with Aman about payment issue</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
+          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6094,17 +5964,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-08T22:49:45.147752+00:00</t>
+          <t>2026-05-09T08:18:42.170906+00:00</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anchit needs access to the vtadmin password for work.</t>
+          <t>To resolve the payment issue and ensure customer satisfaction.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6114,24 +5984,29 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shehzad</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Create Automated Tracker Project</t>
+          <t>Configure Growth Pillar</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Develop an automated project to track and check various aspects of the business.</t>
+          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6146,34 +6021,34 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-09T00:11:20.261831+00:00</t>
+          <t>2026-05-09T08:22:41.106059+00:00</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>To improve efficiency and reduce manual errors.</t>
+          <t>To accurately track and measure growth metrics.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Follow up with Aman about payment issue</t>
+          <t>Update the sheet with old content</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
+          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6188,12 +6063,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-09T08:18:42.170906+00:00</t>
+          <t>2026-05-09T08:24:36.498771+00:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>To resolve the payment issue and ensure customer satisfaction.</t>
+          <t>To ensure that the new sheet is accurate and easy to use.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6203,29 +6078,24 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>ASAP</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Configure Growth Pillar</t>
+          <t>Update status in OOSI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
+          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6240,34 +6110,39 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-09T08:22:41.106059+00:00</t>
+          <t>2026-05-09T08:24:40.831403+00:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>To accurately track and measure growth metrics.</t>
+          <t>To improve task management and avoid confusion.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Update the sheet with old content</t>
+          <t>Implement WhatsApp APIs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
+          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6282,17 +6157,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:36.498771+00:00</t>
+          <t>2026-05-09T08:24:40.843701+00:00</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>To ensure that the new sheet is accurate and easy to use.</t>
+          <t>To leverage WhatsApp for customer engagement and communication.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6309,12 +6184,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Update status in OOSI</t>
+          <t>Explore Google Chat API</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
+          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6329,12 +6204,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:40.831403+00:00</t>
+          <t>2026-05-09T08:28:42.641366+00:00</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>To improve task management and avoid confusion.</t>
+          <t>Using Google Chat API can simplify automation and reduce costs.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6344,7 +6219,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6356,12 +6231,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Implement WhatsApp APIs</t>
+          <t>Create Automated Tracker Project</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6376,17 +6251,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:40.843701+00:00</t>
+          <t>2026-05-09T08:30:38.993816+00:00</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>To leverage WhatsApp for customer engagement and communication.</t>
+          <t>To streamline processes and reduce manual errors.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6403,12 +6278,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Explore Google Chat API</t>
+          <t>Review and address feedback from second meeting with Akhil</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
+          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6423,12 +6298,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-09T08:28:42.641366+00:00</t>
+          <t>2026-05-09T08:32:42.879902+00:00</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Using Google Chat API can simplify automation and reduce costs.</t>
+          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6450,12 +6325,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Create Automated Tracker Project</t>
+          <t>Check and fix PDP page code</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6470,12 +6345,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-09T08:30:38.993816+00:00</t>
+          <t>2026-05-09T08:36:57.281323+00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>To streamline processes and reduce manual errors.</t>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6490,19 +6365,24 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Review and address feedback from second meeting with Akhil</t>
+          <t>Troubleshoot PDP issues on Shopify</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6517,39 +6397,39 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-09T08:32:42.879902+00:00</t>
+          <t>2026-05-09T08:37:14.587514+00:00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Check and fix PDP page code</t>
+          <t>Implement Note-Taking and Task-Making System</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6559,22 +6439,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-09T08:36:57.281323+00:00</t>
+          <t>2026-05-09T10:19:49.277935+00:00</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6585,23 +6465,18 @@
       <c r="K127" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Troubleshoot PDP issues on Shopify</t>
+          <t>Fix HTML coding issue on page deck</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6616,17 +6491,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-09T08:37:14.587514+00:00</t>
+          <t>2026-05-09T10:33:45.601556+00:00</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6643,12 +6518,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Implement Note-Taking and Task-Making System</t>
+          <t>Verify Landing Page Status</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
+          <t>Check the status of the landing pages, including the final URLs, and ensure they are ready to go live by the 6th of May.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6658,44 +6533,56 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-09T10:19:49.277935+00:00</t>
+          <t>2026-05-09T08:31:27.558411+00:00</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
+          <t>To ensure timely launch and meet the marketing goals.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aman</t>
-        </is>
-      </c>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>6th May</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Implement Note-Taking and Task-Making System</t>
+          <t>Review Dashboard Status</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Create a system to store notes and tasks from various sources (discussions, meetings, emails, chats, spaces, groups, WhatsApp chats) in a centralized location (Google Sheets and Excel file) with status update options.</t>
+          <t>Verify the production use of the dashboard and ensure it is ready by the 7th of May.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6705,44 +6592,56 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-09T10:20:08.851294+00:00</t>
+          <t>2026-05-09T08:31:27.568261+00:00</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>To improve productivity and organization by having a single source of truth for notes and tasks.</t>
+          <t>To ensure timely launch and meet the marketing goals.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Aman</t>
-        </is>
-      </c>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fix HTML coding issue on page deck</t>
+          <t>Finalize Creator Partnerships</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
+          <t>Finalize the cadence of creator partnerships and ensure it is completed by the 7th of May.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6752,17 +6651,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-09T10:33:45.601556+00:00</t>
+          <t>2026-05-09T08:31:27.575270+00:00</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
+          <t>To ensure timely launch and meet the marketing goals.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6772,24 +6676,31 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Aman</t>
-        </is>
-      </c>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Verify Landing Page Status</t>
+          <t>Review Pagedeck Status</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Check the status of the landing pages, including the final URLs, and ensure they are ready to go live by the 6th of May.</t>
+          <t>Verify the Pagedeck live on the website and ensure it is ready by the 6th of May.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6809,7 +6720,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.558411+00:00</t>
+          <t>2026-05-09T08:31:27.583295+00:00</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -6843,12 +6754,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Review Dashboard Status</t>
+          <t>Review Dashboard Progress</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Verify the production use of the dashboard and ensure it is ready by the 7th of May.</t>
+          <t>Verify the progress of the production use of the dashboard and ensure it is completed by the specified timeline.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6868,12 +6779,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.568261+00:00</t>
+          <t>2026-05-09T08:31:27.933199+00:00</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>To ensure timely launch and meet the marketing goals.</t>
+          <t>To ensure timely completion of the dashboard and avoid delays in marketing efforts.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6883,7 +6794,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Akhil Arora</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -6902,12 +6813,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Finalize Creator Partnerships</t>
+          <t>Schedule Landing Page Experts Conversation</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Finalize the cadence of creator partnerships and ensure it is completed by the 7th of May.</t>
+          <t>Schedule a final conversation with landing page experts and ensure it is completed by the specified timeline.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6927,33 +6838,33 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.575270+00:00</t>
+          <t>2026-05-09T08:31:27.947556+00:00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>To ensure timely launch and meet the marketing goals.</t>
+          <t>To gather expert insights and drive marketing efforts.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Brand &amp; Content</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Akhil Arora</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>7th May</t>
+          <t>13th May</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -6961,12 +6872,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Review Pagedeck Status</t>
+          <t>Check lending page buttons</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Verify the Pagedeck live on the website and ensure it is ready by the 6th of May.</t>
+          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6981,17 +6892,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.583295+00:00</t>
+          <t>2026-05-09T08:36:22.124156+00:00</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>To ensure timely launch and meet the marketing goals.</t>
+          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7010,22 +6921,18 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>6th May</t>
-        </is>
-      </c>
+      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Review Dashboard Progress</t>
+          <t>Review and confirm updated timelines</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Verify the progress of the production use of the dashboard and ensure it is completed by the specified timeline.</t>
+          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7040,17 +6947,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.933199+00:00</t>
+          <t>2026-05-09T08:36:22.133413+00:00</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>To ensure timely completion of the dashboard and avoid delays in marketing efforts.</t>
+          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7066,25 +6973,21 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>7th May</t>
-        </is>
-      </c>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Schedule Landing Page Experts Conversation</t>
+          <t>Follow up with Aman on lending page issues</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Schedule a final conversation with landing page experts and ensure it is completed by the specified timeline.</t>
+          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7099,27 +7002,27 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0bdca42d83334</t>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-09T08:31:27.947556+00:00</t>
+          <t>2026-05-09T08:36:36.382530+00:00</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>To gather expert insights and drive marketing efforts.</t>
+          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Brand &amp; Content</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Akhil Arora</t>
+          <t>Anchit Tandon</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -7128,22 +7031,18 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>13th May</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Check lending page buttons</t>
+          <t>Add email data to MOM report</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
+          <t>Include email data, cancellations flows, and winback data in the MOM report as requested by Akhil Arora.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7158,22 +7057,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
+          <t>https://mail.google.com/mail/u/0/#inbox/19e0be7680a60500</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-09T08:36:22.124156+00:00</t>
+          <t>2026-05-09T08:43:14.968558+00:00</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
+          <t>To provide a comprehensive view of the business performance.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7184,231 +7083,11 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Review and confirm updated timelines</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Email | from Akhil Arora</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-09T08:36:22.133413+00:00</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Akhil Arora</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Follow up with Aman on lending page issues</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Email | from Akhil Arora</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be151210e740</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-09T08:36:36.382530+00:00</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Anchit Tandon</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Add email data to MOM report</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Include email data, cancellations flows, and winback data in the MOM report as requested by Akhil Arora.</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Email | from Akhil Arora</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be7680a60500</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-09T08:43:14.968558+00:00</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>To provide a comprehensive view of the business performance.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Retention</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Aman Gupta</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Check lending page buttons</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Verify that the lending page buttons are working properly and fix any issues found.</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Email | from Akhil Arora</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be7680a60500</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-09T08:43:19.296925+00:00</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>To ensure a smooth user experience on the lending page.</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Aman Gupta</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7421,7 +7100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7735,11 +7414,6 @@
           <t>Brand &amp; Content</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -7782,11 +7456,6 @@
           <t>Brand &amp; Content</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -7975,11 +7644,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -8022,11 +7686,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -8069,11 +7728,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -8579,11 +8233,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -8626,11 +8275,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -8955,11 +8599,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>High</t>
@@ -9002,11 +8641,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -9049,11 +8683,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -9378,11 +9007,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>High</t>
@@ -9425,11 +9049,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>High</t>
@@ -9472,11 +9091,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>High</t>
@@ -9519,11 +9133,6 @@
           <t>Acquisition</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>High</t>
@@ -9754,11 +9363,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -9994,11 +9598,6 @@
           <t>Retention</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -10041,11 +9640,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Low</t>
@@ -10182,11 +9776,6 @@
           <t>Conversion</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -10511,11 +10100,6 @@
           <t>Retention</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -10572,12 +10156,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Review and Optimize Email Sends</t>
+          <t>Update Product Listings and Availability</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Review the email sends schedule and optimize for better engagement and conversion rates, ensuring no one gets spammed.</t>
+          <t>Update the product listings and availability on the website and Amazon to ensure that customers can easily find and purchase the products mentioned in the email campaign.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10592,39 +10176,39 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.489186+00:00</t>
+          <t>2026-05-08T22:29:09.511333+00:00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>To maximize the impact of the email sprint and achieve the desired revenue goals.</t>
+          <t>To ensure a seamless customer experience and maximize sales opportunities.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monitor and Analyze Email Performance</t>
+          <t>Design the email campaign</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Monitor the email performance and analyze the results to identify areas of improvement and optimize future email campaigns.</t>
+          <t>Create a premium email campaign for VAHDAM India targeting UK customers to drive replenishment and AOV lift by promoting 2-pack bundles.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10639,17 +10223,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.500539+00:00</t>
+          <t>2026-05-08T22:29:41.875777+00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>To understand the effectiveness of the email sprint and make data-driven decisions for future campaigns.</t>
+          <t>Increase customer convenience and drive sales by promoting 2-pack bundles.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10659,19 +10243,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Update Product Listings and Availability</t>
+          <t>Finalize product selection</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Update the product listings and availability on the website and Amazon to ensure that customers can easily find and purchase the products mentioned in the email campaign.</t>
+          <t>Select the two products to feature in the email campaign (Turmeric Ashwagandha 100 Tea Bags and Turmeric Ginger 100 Tea Bags).</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10686,17 +10270,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:09.511333+00:00</t>
+          <t>2026-05-08T22:29:41.881891+00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>To ensure a seamless customer experience and maximize sales opportunities.</t>
+          <t>Ensure the products are relevant and appealing to the target audience.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -10706,19 +10290,19 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Design the email campaign</t>
+          <t>Create a compelling subject line</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Create a premium email campaign for VAHDAM India targeting UK customers to drive replenishment and AOV lift by promoting 2-pack bundles.</t>
+          <t>Craft a subject line that effectively communicates the value proposition of the 2-pack bundle.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10733,12 +10317,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.875777+00:00</t>
+          <t>2026-05-08T22:29:41.886538+00:00</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Increase customer convenience and drive sales by promoting 2-pack bundles.</t>
+          <t>Increase email open rates and drive engagement.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10748,7 +10332,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Arihant</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -10760,12 +10344,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Finalize product selection</t>
+          <t>Create premium DTC email for VAHDAM India (UK market)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Select the two products to feature in the email campaign (Turmeric Ashwagandha 100 Tea Bags and Turmeric Ginger 100 Tea Bags).</t>
+          <t>Design and send a targeted email campaign to active buyers in the UK market, promoting the new iced tea range and highlighting its exclusivity on the VAHDAM website.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10780,39 +10364,44 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.881891+00:00</t>
+          <t>2026-05-08T22:30:00.635644+00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ensure the products are relevant and appealing to the target audience.</t>
+          <t>Drive incremental seasonal purchases from active buyers in the UK market by introducing the new iced tea range and creating a sense of exclusivity.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Create a compelling subject line</t>
+          <t>Check Caption on Amazon</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Craft a subject line that effectively communicates the value proposition of the 2-pack bundle.</t>
+          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10827,22 +10416,22 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-08T22:29:41.886538+00:00</t>
+          <t>2026-05-08T22:30:53.742095+00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Increase email open rates and drive engagement.</t>
+          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Arihant</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10854,12 +10443,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Create premium DTC email for VAHDAM India (UK market)</t>
+          <t>Create Bundle Link</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Design and send a targeted email campaign to active buyers in the UK market, promoting the new iced tea range and highlighting its exclusivity on the VAHDAM website.</t>
+          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10874,44 +10463,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-08T22:30:00.635644+00:00</t>
+          <t>2026-05-08T22:31:06.340431+00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Drive incremental seasonal purchases from active buyers in the UK market by introducing the new iced tea range and creating a sense of exclusivity.</t>
+          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Check Caption on Amazon</t>
+          <t>Work with Aman on Klaviyo Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verify if the specified range is available on Amazon to ensure the caption is accurate.</t>
+          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10926,39 +10510,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-08T22:30:53.742095+00:00</t>
+          <t>2026-05-08T22:31:29.184257+00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Accurate product information is crucial for customer satisfaction and trust.</t>
+          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit Tandon</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Create Bundle Link</t>
+          <t>Review Mailer Creation Document</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Create a link for the bundle that is missing images, and share it with Anchit.</t>
+          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10973,12 +10557,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-08T22:31:06.340431+00:00</t>
+          <t>2026-05-08T22:32:31.890128+00:00</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Missing images are blocking the bundle's visibility, and having a link will help Anchit move forward.</t>
+          <t>To ensure the mailer creation is done correctly and on time.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10988,24 +10572,29 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Work with Aman on Klaviyo Integration</t>
+          <t>Send 1st mailer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Collaborate with Aman to figure out Klaviyo integration and its requirements.</t>
+          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11020,12 +10609,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08T22:31:29.184257+00:00</t>
+          <t>2026-05-08T22:33:33.782561+00:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Klaviyo integration is crucial for retention via email/SMS/WhatsApp.</t>
+          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11035,24 +10624,29 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>As per calendar sheet</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Review Mailer Creation Document</t>
+          <t>Fix Product Page Alignment</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Review the document with feedbacks for mailer creation and ensure it's ready for today.</t>
+          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11067,44 +10661,39 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-08T22:32:31.890128+00:00</t>
+          <t>2026-05-08T22:34:13.184575+00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>To ensure the mailer creation is done correctly and on time.</t>
+          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Send 1st mailer</t>
+          <t>Correct Grammar in Product Selection</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
+          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11119,17 +10708,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-08T22:33:33.782561+00:00</t>
+          <t>2026-05-08T22:34:13.194823+00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
+          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -11139,24 +10728,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>As per calendar sheet</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Fix Product Page Alignment</t>
+          <t>Fix Broken CTAs</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
+          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11171,12 +10755,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.184575+00:00</t>
+          <t>2026-05-08T22:34:13.207312+00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
+          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11198,12 +10782,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Correct Grammar in Product Selection</t>
+          <t>Finalize Mother's Day Gift Ideas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
+          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11218,17 +10802,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.194823+00:00</t>
+          <t>2026-05-08T22:34:24.039065+00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
+          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -11239,18 +10823,23 @@
       <c r="K79" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Before Mother's Day</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fix Broken CTAs</t>
+          <t>Create Email Subject Lines</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
+          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11265,39 +10854,44 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:13.207312+00:00</t>
+          <t>2026-05-08T22:34:24.049162+00:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
+          <t>To grab customers' attention and increase email open rates.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Before sending Mother's Day emails</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Finalize Mother's Day Gift Ideas</t>
+          <t>Finalize Email Campaign for First Flush Tea</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
+          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11312,17 +10906,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:24.039065+00:00</t>
+          <t>2026-05-08T22:34:52.148970+00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
+          <t>Increase sales and revenue by promoting a high-demand product.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>AOV</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -11337,19 +10931,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Before Mother's Day</t>
+          <t>Go Live</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Create Email Subject Lines</t>
+          <t>Review UK Consumer Emails</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
+          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11364,44 +10958,39 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:24.049162+00:00</t>
+          <t>2026-05-08T22:35:34.120456+00:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>To grab customers' attention and increase email open rates.</t>
+          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Before sending Mother's Day emails</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Finalize Email Campaign for First Flush Tea</t>
+          <t>Review Cancellation Flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
+          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11416,17 +11005,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-08T22:34:52.148970+00:00</t>
+          <t>2026-05-08T22:35:34.131514+00:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Increase sales and revenue by promoting a high-demand product.</t>
+          <t>To ensure a smooth customer experience and minimize cancellations.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -11436,24 +11025,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Go Live</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Review UK Consumer Emails</t>
+          <t>Take Screenshots of Campaigns</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
+          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11468,12 +11052,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.120456+00:00</t>
+          <t>2026-05-08T22:35:34.139460+00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
+          <t>To document the current state of email marketing campaigns.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -11495,12 +11079,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Review Cancellation Flow</t>
+          <t>Verify Hibiscus Rose Discount Consistency</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
+          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11515,39 +11099,39 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.131514+00:00</t>
+          <t>2026-05-08T22:35:46.978363+00:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>To ensure a smooth customer experience and minimize cancellations.</t>
+          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Take Screenshots of Campaigns</t>
+          <t>Retain Email Flow Documentation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
+          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11562,12 +11146,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:34.139460+00:00</t>
+          <t>2026-05-08T22:35:56.509833+00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>To document the current state of email marketing campaigns.</t>
+          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -11577,7 +11161,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11589,12 +11173,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Verify Hibiscus Rose Discount Consistency</t>
+          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
+          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11609,39 +11193,34 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:46.978363+00:00</t>
+          <t>2026-05-08T22:36:05.582729+00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
+          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Anchit</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Retain Email Flow Documentation</t>
+          <t>Implement nudges on Vahdam India's PDP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
+          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -11656,22 +11235,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08T22:35:56.509833+00:00</t>
+          <t>2026-05-08T22:36:05.597638+00:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
+          <t>To increase average order value and encourage users to explore more products.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Retention</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Manisha</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11683,12 +11257,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
+          <t>Develop a recommendation engine for Vahdam India's website</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
+          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11703,22 +11277,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.582729+00:00</t>
+          <t>2026-05-08T22:36:05.606317+00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
+          <t>To increase sales and improve customer satisfaction.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -11730,12 +11299,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Implement nudges on Vahdam India's PDP</t>
+          <t>Analyze customer support queries to identify areas for improvement</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
+          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11750,22 +11319,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.597638+00:00</t>
+          <t>2026-05-08T22:36:05.612573+00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>To increase average order value and encourage users to explore more products.</t>
+          <t>To improve customer satisfaction and reduce support queries.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>AOV</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>users/110152155675645013355</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11777,12 +11341,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Develop a recommendation engine for Vahdam India's website</t>
+          <t>Request for Quote (RFQ)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
+          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11797,22 +11361,22 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.606317+00:00</t>
+          <t>2026-05-08T22:36:56.953122+00:00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>To increase sales and improve customer satisfaction.</t>
+          <t>To get a clear understanding of the agency's services and fees.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>users/110152155675645013355</t>
+          <t>Anchit Tandon</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11824,12 +11388,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Analyze customer support queries to identify areas for improvement</t>
+          <t>Discuss View-Only Access with Agency</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
+          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11844,22 +11408,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:05.612573+00:00</t>
+          <t>2026-05-08T22:36:56.961722+00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>To improve customer satisfaction and reduce support queries.</t>
+          <t>To ensure seamless collaboration and minimize potential issues.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>users/110152155675645013355</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11871,12 +11435,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Request for Quote (RFQ)</t>
+          <t>Prepare Quotation Slab</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
+          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -11891,12 +11455,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.953122+00:00</t>
+          <t>2026-05-08T22:36:56.967275+00:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>To get a clear understanding of the agency's services and fees.</t>
+          <t>To ensure transparency and clarity in the agency's fees.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11906,7 +11470,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11918,12 +11482,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Discuss View-Only Access with Agency</t>
+          <t>Create Production-Ready HTML</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
+          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -11938,17 +11502,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.961722+00:00</t>
+          <t>2026-05-08T22:39:50.956188+00:00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>To ensure seamless collaboration and minimize potential issues.</t>
+          <t>To ensure the content is ready for use in the production environment.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11965,12 +11529,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Prepare Quotation Slab</t>
+          <t>Set 2-hour timer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
+          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11985,17 +11549,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-08T22:36:56.967275+00:00</t>
+          <t>2026-05-08T22:40:15.847487+00:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>To ensure transparency and clarity in the agency's fees.</t>
+          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -12006,18 +11570,23 @@
       <c r="K95" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2 hours</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Create Production-Ready HTML</t>
+          <t>Host Images on Shopify</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
+          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -12032,17 +11601,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-08T22:39:50.956188+00:00</t>
+          <t>2026-05-08T22:40:35.933949+00:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>To ensure the content is ready for use in the production environment.</t>
+          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12052,19 +11621,19 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Set 2-hour timer</t>
+          <t>Host HTMLs on Shopify</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
+          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -12079,17 +11648,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-08T22:40:15.847487+00:00</t>
+          <t>2026-05-08T22:41:13.063844+00:00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
+          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12100,23 +11669,18 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>2 hours</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Host Images on Shopify</t>
+          <t>Review UK Landing Pages</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
+          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12126,22 +11690,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Chat | Google Chat</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-08T22:40:35.933949+00:00</t>
+          <t>2026-05-08T22:43:53.526856+00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
+          <t>To improve conversion rates on the UK website.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12151,19 +11715,19 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Host HTMLs on Shopify</t>
+          <t>Update Canada-Specific Content</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
+          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12173,27 +11737,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Chat | Google Chat</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-08T22:41:13.063844+00:00</t>
+          <t>2026-05-08T22:43:53.558663+00:00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
+          <t>To improve the user experience for Canadian customers.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -12205,12 +11769,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Review UK Landing Pages</t>
+          <t>Review Nutrition Support Pages</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
+          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12225,39 +11789,39 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.526856+00:00</t>
+          <t>2026-05-08T22:43:53.570620+00:00</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>To improve conversion rates on the UK website.</t>
+          <t>To improve customer engagement and retention.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Arihant</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Update Canada-Specific Content</t>
+          <t>Provide UK Data in Specified Format</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
+          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -12272,39 +11836,44 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.558663+00:00</t>
+          <t>2026-05-08T22:44:12.623888+00:00</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>To improve the user experience for Canadian customers.</t>
+          <t>Anchit needs this data for analysis and decision-making.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Review Nutrition Support Pages</t>
+          <t>Prepare Price Parity Sheet</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
+          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12314,44 +11883,49 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:53.570620+00:00</t>
+          <t>2026-05-08T22:45:13.665247+00:00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>To improve customer engagement and retention.</t>
+          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Arihant</t>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>101892413922856</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Provide UK Data in Specified Format</t>
+          <t>Update on Gorilla sheet</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
+          <t>Get an update on the current status of the Gorilla sheet.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12361,49 +11935,44 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Chat | DM with users/101892413922856052375</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-08T22:44:12.623888+00:00</t>
+          <t>2026-05-08T22:45:22.145961+00:00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Anchit needs this data for analysis and decision-making.</t>
+          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Aman</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>101892413922856</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>As soon as possible</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prepare Price Parity Sheet</t>
+          <t>Research Amazon Pricing</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
+          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12418,12 +11987,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:13.665247+00:00</t>
+          <t>2026-05-08T22:45:39.720118+00:00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
+          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12443,19 +12012,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Update on Gorilla sheet</t>
+          <t>Complete App Creation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Get an update on the current status of the Gorilla sheet.</t>
+          <t>Anchit needs to finish creating his app by the weekend.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12465,49 +12034,49 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Chat | DM with users/101892413922856052375</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:22.145961+00:00</t>
+          <t>2026-05-08T22:45:50.944684+00:00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
+          <t>App creation is a priority to move forward with new features and revenue growth.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>users/101892413922856052375</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>101892413922856</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>by the weekend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Research Amazon Pricing</t>
+          <t>Review Email List and Body</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
+          <t>Review the email list and body sent by the user and take necessary actions.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12517,22 +12086,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chat | DM with users/101892413922856052375</t>
+          <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:39.720118+00:00</t>
+          <t>2026-05-08T22:46:55.532712+00:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
+          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12542,7 +12111,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>101892413922856</t>
+          <t>112363631041538</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12554,12 +12123,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Complete App Creation</t>
+          <t>Follow up on user query</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Anchit needs to finish creating his app by the weekend.</t>
+          <t>Respond to the user's query in the DM.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12569,49 +12138,49 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
+          <t>Chat | DM with users/112363631041538884730</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:50.944684+00:00</t>
+          <t>2026-05-08T22:47:18.396185+00:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>App creation is a priority to move forward with new features and revenue growth.</t>
+          <t>Address the user's concern to provide a good customer experience.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>112363631041538</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>by the weekend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Review Email List and Body</t>
+          <t>Check Something</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Review the email list and body sent by the user and take necessary actions.</t>
+          <t>The recipient needs to check something as requested by Anchit.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12626,22 +12195,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-08T22:46:55.532712+00:00</t>
+          <t>2026-05-08T22:47:30.899202+00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
+          <t>Anchit needs this checked to move forward.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Anchit (Self)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12658,12 +12222,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Follow up on user query</t>
+          <t>Send requested file</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Respond to the user's query in the DM.</t>
+          <t>Send the requested file to the user today.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12678,17 +12242,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:18.396185+00:00</t>
+          <t>2026-05-08T22:47:40.411387+00:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Address the user's concern to provide a good customer experience.</t>
+          <t>Meet the user's request to send the file today.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12704,18 +12268,23 @@
       <c r="K109" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Today</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Check Something</t>
+          <t>Share the item by night</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The recipient needs to check something as requested by Anchit.</t>
+          <t>Share the item with the recipient by the end of the day.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12730,12 +12299,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:30.899202+00:00</t>
+          <t>2026-05-08T22:48:07.925411+00:00</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anchit needs this checked to move forward.</t>
+          <t>The recipient is waiting for the item to be shared.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12745,7 +12314,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>users/112363631041538884730</t>
+          <t>Anchit (Self)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12756,18 +12325,23 @@
       <c r="K110" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>by night</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Send requested file</t>
+          <t>Follow up on salary account opening</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Send the requested file to the user today.</t>
+          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12777,17 +12351,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Chat | DM with users/112363631041538884730</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-08T22:47:40.411387+00:00</t>
+          <t>2026-05-08T22:48:35.348293+00:00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Meet the user's request to send the file today.</t>
+          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12797,34 +12371,24 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>112363631041538</t>
+          <t>Subham</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Today</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Share the item by night</t>
+          <t>Schedule Meeting</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Share the item with the recipient by the end of the day.</t>
+          <t>Schedule a meeting with Aman to discuss the same topic.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12834,32 +12398,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Chat | DM with users/112363631041538884730</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:07.925411+00:00</t>
+          <t>2026-05-08T22:48:42.866232+00:00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>The recipient is waiting for the item to be shared.</t>
+          <t>Need to discuss something with Aman.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>112363631041538</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -12869,19 +12428,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>by night</t>
+          <t>As soon as possible</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Follow up on salary account opening</t>
+          <t>Update on Current Status</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
+          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12896,12 +12455,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:35.348293+00:00</t>
+          <t>2026-05-08T22:48:47.346443+00:00</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
+          <t>Anchit needs to stay informed about the topic.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12916,19 +12475,19 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Schedule Meeting</t>
+          <t>Provide VTAdmin account password</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Schedule a meeting with Aman to discuss the same topic.</t>
+          <t>Share the admin account password (VTAdmin) with Shehzad to help with installing Claude.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12943,12 +12502,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:42.866232+00:00</t>
+          <t>2026-05-08T22:48:54.415129+00:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Need to discuss something with Aman.</t>
+          <t>Installing Claude requires the admin account password to proceed.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12958,29 +12517,24 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Shehzad</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>As soon as possible</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Update on Current Status</t>
+          <t>Provide vtadmin password</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
+          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12995,22 +12549,22 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:47.346443+00:00</t>
+          <t>2026-05-08T22:49:45.147752+00:00</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anchit needs to stay informed about the topic.</t>
+          <t>Anchit needs access to the vtadmin password for work.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Subham</t>
+          <t>Shehzad</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -13022,12 +12576,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Provide VTAdmin account password</t>
+          <t>Create Automated Tracker Project</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Share the admin account password (VTAdmin) with Shehzad to help with installing Claude.</t>
+          <t>Develop an automated project to track and check various aspects of the business.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13037,44 +12591,39 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-08T22:48:54.415129+00:00</t>
+          <t>2026-05-09T00:11:20.261831+00:00</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Installing Claude requires the admin account password to proceed.</t>
+          <t>To improve efficiency and reduce manual errors.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Team &amp; Process</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Shehzad</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Provide vtadmin password</t>
+          <t>Follow up with Aman about payment issue</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
+          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -13084,17 +12633,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Chat | DM</t>
+          <t>Meeting | voice memo by Anchit (Self)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-08T22:49:45.147752+00:00</t>
+          <t>2026-05-09T08:18:42.170906+00:00</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anchit needs access to the vtadmin password for work.</t>
+          <t>To resolve the payment issue and ensure customer satisfaction.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13104,24 +12653,29 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shehzad</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Create Automated Tracker Project</t>
+          <t>Configure Growth Pillar</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Develop an automated project to track and check various aspects of the business.</t>
+          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13136,34 +12690,34 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-09T00:11:20.261831+00:00</t>
+          <t>2026-05-09T08:22:41.106059+00:00</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>To improve efficiency and reduce manual errors.</t>
+          <t>To accurately track and measure growth metrics.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Follow up with Aman about payment issue</t>
+          <t>Update the sheet with old content</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
+          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13178,12 +12732,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-09T08:18:42.170906+00:00</t>
+          <t>2026-05-09T08:24:36.498771+00:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>To resolve the payment issue and ensure customer satisfaction.</t>
+          <t>To ensure that the new sheet is accurate and easy to use.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -13193,29 +12747,24 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>ASAP</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Configure Growth Pillar</t>
+          <t>Update status in OOSI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
+          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13230,34 +12779,39 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-09T08:22:41.106059+00:00</t>
+          <t>2026-05-09T08:24:40.831403+00:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>To accurately track and measure growth metrics.</t>
+          <t>To improve task management and avoid confusion.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Update the sheet with old content</t>
+          <t>Implement WhatsApp APIs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
+          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13272,17 +12826,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:36.498771+00:00</t>
+          <t>2026-05-09T08:24:40.843701+00:00</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>To ensure that the new sheet is accurate and easy to use.</t>
+          <t>To leverage WhatsApp for customer engagement and communication.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -13299,12 +12853,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Update status in OOSI</t>
+          <t>Explore Google Chat API</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
+          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13319,12 +12873,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:40.831403+00:00</t>
+          <t>2026-05-09T08:28:42.641366+00:00</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>To improve task management and avoid confusion.</t>
+          <t>Using Google Chat API can simplify automation and reduce costs.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13334,7 +12888,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Aman</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -13346,12 +12900,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Implement WhatsApp APIs</t>
+          <t>Create Automated Tracker Project</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13366,17 +12920,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-09T08:24:40.843701+00:00</t>
+          <t>2026-05-09T08:30:38.993816+00:00</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>To leverage WhatsApp for customer engagement and communication.</t>
+          <t>To streamline processes and reduce manual errors.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -13393,12 +12947,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Explore Google Chat API</t>
+          <t>Review and address feedback from second meeting with Akhil</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
+          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -13413,12 +12967,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-09T08:28:42.641366+00:00</t>
+          <t>2026-05-09T08:32:42.879902+00:00</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Using Google Chat API can simplify automation and reduce costs.</t>
+          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13440,12 +12994,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Create Automated Tracker Project</t>
+          <t>Check and fix PDP page code</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -13460,12 +13014,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-09T08:30:38.993816+00:00</t>
+          <t>2026-05-09T08:36:57.281323+00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>To streamline processes and reduce manual errors.</t>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13480,19 +13034,24 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Review and address feedback from second meeting with Akhil</t>
+          <t>Troubleshoot PDP issues on Shopify</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -13507,39 +13066,39 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-09T08:32:42.879902+00:00</t>
+          <t>2026-05-09T08:37:14.587514+00:00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Anchit</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Check and fix PDP page code</t>
+          <t>Implement Note-Taking and Task-Making System</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13549,22 +13108,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
+          <t>Chat | DM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-09T08:36:57.281323+00:00</t>
+          <t>2026-05-09T10:19:49.277935+00:00</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Team &amp; Process</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -13575,23 +13134,18 @@
       <c r="K127" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Troubleshoot PDP issues on Shopify</t>
+          <t>Fix HTML coding issue on page deck</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13606,17 +13160,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-09T08:37:14.587514+00:00</t>
+          <t>2026-05-09T10:33:45.601556+00:00</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -13625,147 +13179,6 @@
         </is>
       </c>
       <c r="K128" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Implement Note-Taking and Task-Making System</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Chat | DM</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-09T10:19:49.277935+00:00</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Team &amp; Process</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Aman</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Implement Note-Taking and Task-Making System</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Create a system to store notes and tasks from various sources (discussions, meetings, emails, chats, spaces, groups, WhatsApp chats) in a centralized location (Google Sheets and Excel file) with status update options.</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Chat | DM</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-09T10:20:08.851294+00:00</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>To improve productivity and organization by having a single source of truth for notes and tasks.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Team &amp; Process</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Aman</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Fix HTML coding issue on page deck</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Meeting | voice memo by Anchit (Self)</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-09T10:33:45.601556+00:00</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Aman</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -13782,7 +13195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -14417,58 +13830,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Check lending page buttons</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Verify that the lending page buttons are working properly and fix any issues found.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Email | from Akhil Arora</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://mail.google.com/mail/u/0/#inbox/19e0be7680a60500</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-09T08:43:19.296925+00:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>To ensure a smooth user experience on the lending page.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Aman Gupta</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14480,7 +13841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14545,6 +13906,11 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>All Updates</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -14561,7 +13927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14626,6 +13992,11 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>All Updates</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -14642,7 +14013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14707,6 +14078,11 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>All Updates</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -14723,7 +14099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14789,6 +14165,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>All Updates</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Remarks</t>
         </is>
       </c>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Anchit (Self)</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Anchit Tandon</t>
+          <t>Anchit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aman Gupta</t>
+          <t>Aman</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
